--- a/output/graficos_nacionales/plot_nacional_serie_i_ingr_mean_s_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_ingr_mean_s_2023.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:21</t>
+    <t xml:space="preserve">2026-10-05 18:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -492,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
